--- a/balance_generate/output_data/8_transactions.xlsx
+++ b/balance_generate/output_data/8_transactions.xlsx
@@ -425,422 +425,2130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>bs_side</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>balance_amt</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>client_type_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>rate_type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>current_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>7087739.393393129</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0500210000001</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5897730.22</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>7532896.262694715</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>0500210000002</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10113123.61</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>6401311.972722309</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0500210000003</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11299498.54</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>8618071.204924984</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0500210000004</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>10959817.29</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>7868857.565613141</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>0500210000005</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5317623.76</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>8884421.794517225</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0500210000006</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4043030.98</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>6977406.92209777</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>8</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0500210000007</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6941225.35</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>9691629.315412935</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>0500210000008</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3076863.35</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>6305561.251689039</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0500210000009</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11879063.12</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>6401102.217027714</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0500210000010</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>5226595.62</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>8140172.113504727</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0500210000011</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3492606.83</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>4856794.862525795</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0500210000012</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5294896.05</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>10335432.46397462</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>8</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0500210000013</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9602483.890000001</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>8146325.017623786</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0500210000014</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12502509.24</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>7804736.953353833</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>8</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0500210000015</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8655409.960000001</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>10599473.0949308</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>8</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0500210000016</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7328590.81</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>6375320.992041667</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0500210000017</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7325031.37</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>11293974.13051017</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>8</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0500210000018</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5218356.83</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>7590196.604286529</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0500210000019</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6003759.57</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>4900216.29353307</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0500210000020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4796123.12</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>11210951.27825665</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0500210000021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>8955546.859999999</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>8</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>5940450.118499473</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0500210000022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11861172.92</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6682458.956953702</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0500210000023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5692138.82</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>2353448.736497564</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>8</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0500210000024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>8374301.81</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>4417026.087917236</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0500210000025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>6598776.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>2869321.425666785</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0500210000026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>8128258.64</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>8</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>8770139.613297068</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>8</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0500210000027</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13199356.81</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>1944563.356533587</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>8</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0500210000028</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4436766.75</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0500210000029</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7120649.04</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0500210000030</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>6628672.81</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0500210000031</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>4460283.05</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0500210000032</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7508039.76</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0500210000033</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>7671009.48</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0500210000034</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>12342780.75</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0500210000035</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11815423.53</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0500210000036</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>7870490.91</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>8</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0500210000037</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>9627750.58</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>8</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0500210000038</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3990949.48</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0500210000039</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8988435.57</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0500210000040</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6796957.47</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0500210000041</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7867984.35</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0500210000042</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7238383.61</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>8</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0500210000043</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3819877.66</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0500210000044</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8291507.33</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>8</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0500210000045</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>9303648.33</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0500210000046</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7481269.37</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0500210000047</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>7518518.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0500210000048</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>9983535.26</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0500210000049</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10841693.32</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0500210000050</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10132958.88</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0500210000051</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>8991207.789999999</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0500210000052</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>7185382.49</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0500210000053</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2485288.78</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0500210000054</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11044615.36</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0500210000055</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6675352.75</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>8</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0500210000056</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7748891.58</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>8</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0500210000057</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>6365207.71</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>8</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0500210000058</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10813474.61</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>8</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0500210000059</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>9853368.470000001</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>8</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0500210000060</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>8623152.75</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0500210000061</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6761631.17</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0500210000062</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>6121293.51</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>8</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0500210000063</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>6267495.68</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0500210000064</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>6218297.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>8</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0500210000065</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>5323862.689999998</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
